--- a/inst/extdata/DBSetup.xlsx
+++ b/inst/extdata/DBSetup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="3308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3310" uniqueCount="3310">
   <si>
     <t xml:space="preserve">Database</t>
   </si>
@@ -9938,6 +9938,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://wwwn.cdc.gov/Nchs/Data/Nhanes/Public/2021/DataFiles/VOCWB_L.xpt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"MalformedRowPolicy":"trim_trailing_missing"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"HeaderDuplicatePolicy":"drop_redundant"}</t>
   </si>
 </sst>
 </file>
@@ -13625,7 +13631,9 @@
       <c r="M50" t="s">
         <v>35</v>
       </c>
-      <c r="N50"/>
+      <c r="N50" t="s">
+        <v>3308</v>
+      </c>
       <c r="O50" t="s">
         <v>198</v>
       </c>
@@ -14039,7 +14047,9 @@
       <c r="M56" t="s">
         <v>35</v>
       </c>
-      <c r="N56"/>
+      <c r="N56" t="s">
+        <v>3309</v>
+      </c>
       <c r="O56" t="s">
         <v>198</v>
       </c>
